--- a/data/italy/p4_modeling/2024-10-15/df_best_model.xlsx
+++ b/data/italy/p4_modeling/2024-10-15/df_best_model.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,25 +537,25 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>131</v>
+        <v>527</v>
       </c>
       <c r="B2" t="n">
-        <v>1.382424792913295</v>
+        <v>0.09159182244785655</v>
       </c>
       <c r="C2" t="n">
-        <v>11.89396665824496</v>
+        <v>8.709341444362128</v>
       </c>
       <c r="D2" t="n">
-        <v>10.48017921118692</v>
+        <v>7.789434700130494</v>
       </c>
       <c r="E2" t="n">
-        <v>2332.33402754675</v>
+        <v>3513.76469422001</v>
       </c>
       <c r="F2" t="n">
-        <v>13.71961192674559</v>
+        <v>20.66920408364712</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -564,7 +564,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>(170, 50)</t>
+          <t>(170, 23)</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0.1534933904691156</v>
+        <v>1.373222386065371</v>
       </c>
       <c r="O2" t="n">
         <v>63</v>
@@ -598,42 +598,42 @@
         <v>46</v>
       </c>
       <c r="R2" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="S2" t="n">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="T2" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="U2" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="V2" t="n">
-        <v>47.64705882352941</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>59</v>
+        <v>131</v>
       </c>
       <c r="B3" t="n">
-        <v>1.57639637693388</v>
+        <v>1.382424792913295</v>
       </c>
       <c r="C3" t="n">
-        <v>2.516693569308623</v>
+        <v>11.89396665824496</v>
       </c>
       <c r="D3" t="n">
-        <v>9.016119680734592</v>
+        <v>10.48017921118692</v>
       </c>
       <c r="E3" t="n">
-        <v>706.3540942754244</v>
+        <v>2332.33402754675</v>
       </c>
       <c r="F3" t="n">
-        <v>4.155024083973085</v>
+        <v>13.71961192674559</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -655,7 +655,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>(170, 31)</t>
+          <t>(170, 50)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.6509852985854525</v>
+        <v>0.1534933904691156</v>
       </c>
       <c r="O3" t="n">
         <v>63</v>
@@ -676,42 +676,42 @@
         <v>46</v>
       </c>
       <c r="R3" t="n">
+        <v>63</v>
+      </c>
+      <c r="S3" t="n">
+        <v>82</v>
+      </c>
+      <c r="T3" t="n">
+        <v>25</v>
+      </c>
+      <c r="U3" t="n">
         <v>81</v>
       </c>
-      <c r="S3" t="n">
-        <v>72</v>
-      </c>
-      <c r="T3" t="n">
-        <v>17</v>
-      </c>
-      <c r="U3" t="n">
-        <v>70</v>
-      </c>
       <c r="V3" t="n">
-        <v>41.17647058823529</v>
+        <v>47.64705882352941</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B4" t="n">
-        <v>-1.098196233930086</v>
+        <v>1.57639637693388</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2537775332808732</v>
+        <v>2.516693569308623</v>
       </c>
       <c r="D4" t="n">
-        <v>1.470384030136981</v>
+        <v>9.016119680734592</v>
       </c>
       <c r="E4" t="n">
-        <v>469.7761070615351</v>
+        <v>706.3540942754244</v>
       </c>
       <c r="F4" t="n">
-        <v>2.763388865067853</v>
+        <v>4.155024083973085</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>(170, 35)</t>
+          <t>(170, 31)</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -742,7 +742,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>9.88902090481516</v>
+        <v>0.6509852985854525</v>
       </c>
       <c r="O4" t="n">
         <v>63</v>
@@ -754,42 +754,42 @@
         <v>46</v>
       </c>
       <c r="R4" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="S4" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="T4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="U4" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="V4" t="n">
-        <v>48.23529411764706</v>
+        <v>41.17647058823529</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B5" t="n">
-        <v>-1.3603706273069</v>
+        <v>-1.098196233930086</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2661930899976195</v>
+        <v>0.2537775332808732</v>
       </c>
       <c r="D5" t="n">
-        <v>1.180387177185768</v>
+        <v>1.470384030136981</v>
       </c>
       <c r="E5" t="n">
-        <v>244.5029454110955</v>
+        <v>469.7761070615351</v>
       </c>
       <c r="F5" t="n">
-        <v>1.438252620065268</v>
+        <v>2.763388865067853</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.25</v>
+        <v>-0.5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -811,7 +811,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>(170, 24)</t>
+          <t>(170, 35)</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>4.403042656284315</v>
+        <v>9.88902090481516</v>
       </c>
       <c r="O5" t="n">
         <v>63</v>
@@ -832,18 +832,96 @@
         <v>46</v>
       </c>
       <c r="R5" t="n">
+        <v>73</v>
+      </c>
+      <c r="S5" t="n">
+        <v>78</v>
+      </c>
+      <c r="T5" t="n">
+        <v>19</v>
+      </c>
+      <c r="U5" t="n">
+        <v>82</v>
+      </c>
+      <c r="V5" t="n">
+        <v>48.23529411764706</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-1.3603706273069</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.2661930899976195</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.180387177185768</v>
+      </c>
+      <c r="E6" t="n">
+        <v>244.5029454110955</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.438252620065268</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>kelly</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>(170, 24)</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="N6" t="n">
+        <v>4.403042656284315</v>
+      </c>
+      <c r="O6" t="n">
+        <v>63</v>
+      </c>
+      <c r="P6" t="n">
+        <v>61</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>46</v>
+      </c>
+      <c r="R6" t="n">
         <v>70</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S6" t="n">
         <v>86</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>14</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U6" t="n">
         <v>76</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V6" t="n">
         <v>44.70588235294118</v>
       </c>
     </row>

--- a/data/italy/p4_modeling/2024-10-15/df_best_model.xlsx
+++ b/data/italy/p4_modeling/2024-10-15/df_best_model.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,16 +543,16 @@
         <v>0.09159182244785655</v>
       </c>
       <c r="C2" t="n">
-        <v>8.709341444362128</v>
+        <v>8.709341444362126</v>
       </c>
       <c r="D2" t="n">
         <v>7.789434700130494</v>
       </c>
       <c r="E2" t="n">
-        <v>3513.76469422001</v>
+        <v>7407.769054102303</v>
       </c>
       <c r="F2" t="n">
-        <v>20.66920408364712</v>
+        <v>41.3841846597894</v>
       </c>
       <c r="G2" t="n">
         <v>-0.25</v>
@@ -562,22 +562,18 @@
           <t>kelly</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="I2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
       </c>
       <c r="K2" t="b">
         <v>1</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>(170, 23)</t>
+          <t>(179, 23)</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -586,76 +582,72 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>1.373222386065371</v>
+        <v>3.751700794390016</v>
       </c>
       <c r="O2" t="n">
+        <v>66</v>
+      </c>
+      <c r="P2" t="n">
         <v>63</v>
       </c>
-      <c r="P2" t="n">
-        <v>61</v>
-      </c>
       <c r="Q2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="R2" t="n">
+        <v>75</v>
+      </c>
+      <c r="S2" t="n">
         <v>71</v>
       </c>
-      <c r="S2" t="n">
-        <v>69</v>
-      </c>
       <c r="T2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="U2" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="V2" t="n">
-        <v>50</v>
+        <v>51.39664804469274</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>131</v>
+        <v>228</v>
       </c>
       <c r="B3" t="n">
-        <v>1.382424792913295</v>
+        <v>-1.18858559318555</v>
       </c>
       <c r="C3" t="n">
-        <v>11.89396665824496</v>
+        <v>1.239957012858478</v>
       </c>
       <c r="D3" t="n">
-        <v>10.48017921118692</v>
+        <v>0.9778454372858792</v>
       </c>
       <c r="E3" t="n">
-        <v>2332.33402754675</v>
+        <v>288.387955394816</v>
       </c>
       <c r="F3" t="n">
-        <v>13.71961192674559</v>
+        <v>1.611105896060425</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>kelly</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="I3" t="n">
+        <v>20</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
       </c>
       <c r="K3" t="b">
         <v>1</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>(170, 50)</t>
+          <t>(179, 66)</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -664,265 +656,31 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0.1534933904691156</v>
+        <v>0.2993239921651283</v>
       </c>
       <c r="O3" t="n">
+        <v>66</v>
+      </c>
+      <c r="P3" t="n">
         <v>63</v>
       </c>
-      <c r="P3" t="n">
-        <v>61</v>
-      </c>
       <c r="Q3" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="R3" t="n">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="S3" t="n">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="T3" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="U3" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="V3" t="n">
-        <v>47.64705882352941</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>59</v>
-      </c>
-      <c r="B4" t="n">
-        <v>1.57639637693388</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2.516693569308623</v>
-      </c>
-      <c r="D4" t="n">
-        <v>9.016119680734592</v>
-      </c>
-      <c r="E4" t="n">
-        <v>706.3540942754244</v>
-      </c>
-      <c r="F4" t="n">
-        <v>4.155024083973085</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>kelly</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" t="b">
-        <v>1</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>(170, 31)</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>XGBClassifier</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>0.6509852985854525</v>
-      </c>
-      <c r="O4" t="n">
-        <v>63</v>
-      </c>
-      <c r="P4" t="n">
-        <v>61</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>46</v>
-      </c>
-      <c r="R4" t="n">
-        <v>81</v>
-      </c>
-      <c r="S4" t="n">
-        <v>72</v>
-      </c>
-      <c r="T4" t="n">
-        <v>17</v>
-      </c>
-      <c r="U4" t="n">
-        <v>70</v>
-      </c>
-      <c r="V4" t="n">
-        <v>41.17647058823529</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>67</v>
-      </c>
-      <c r="B5" t="n">
-        <v>-1.098196233930086</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.2537775332808732</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1.470384030136981</v>
-      </c>
-      <c r="E5" t="n">
-        <v>469.7761070615351</v>
-      </c>
-      <c r="F5" t="n">
-        <v>2.763388865067853</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>kelly</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" t="b">
-        <v>1</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>(170, 35)</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>XGBClassifier</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>9.88902090481516</v>
-      </c>
-      <c r="O5" t="n">
-        <v>63</v>
-      </c>
-      <c r="P5" t="n">
-        <v>61</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>46</v>
-      </c>
-      <c r="R5" t="n">
-        <v>73</v>
-      </c>
-      <c r="S5" t="n">
-        <v>78</v>
-      </c>
-      <c r="T5" t="n">
-        <v>19</v>
-      </c>
-      <c r="U5" t="n">
-        <v>82</v>
-      </c>
-      <c r="V5" t="n">
-        <v>48.23529411764706</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>69</v>
-      </c>
-      <c r="B6" t="n">
-        <v>-1.3603706273069</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.2661930899976195</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.180387177185768</v>
-      </c>
-      <c r="E6" t="n">
-        <v>244.5029454110955</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1.438252620065268</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>kelly</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>(170, 24)</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>XGBClassifier</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>4.403042656284315</v>
-      </c>
-      <c r="O6" t="n">
-        <v>63</v>
-      </c>
-      <c r="P6" t="n">
-        <v>61</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>46</v>
-      </c>
-      <c r="R6" t="n">
-        <v>70</v>
-      </c>
-      <c r="S6" t="n">
-        <v>86</v>
-      </c>
-      <c r="T6" t="n">
-        <v>14</v>
-      </c>
-      <c r="U6" t="n">
-        <v>76</v>
-      </c>
-      <c r="V6" t="n">
-        <v>44.70588235294118</v>
+        <v>43.5754189944134</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p4_modeling/2024-10-15/df_best_model.xlsx
+++ b/data/italy/p4_modeling/2024-10-15/df_best_model.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="B1:Q1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>% ROI 100</t>
+          <t>% roi_100</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
@@ -508,179 +508,6 @@
         <is>
           <t># result 2</t>
         </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t># pred 1</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t># pred 0</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t># pred 2</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t># aciertos</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>precision</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>527</v>
-      </c>
-      <c r="B2" t="n">
-        <v>0.09159182244785655</v>
-      </c>
-      <c r="C2" t="n">
-        <v>8.709341444362126</v>
-      </c>
-      <c r="D2" t="n">
-        <v>7.789434700130494</v>
-      </c>
-      <c r="E2" t="n">
-        <v>7407.769054102303</v>
-      </c>
-      <c r="F2" t="n">
-        <v>41.3841846597894</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>kelly</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>(179, 23)</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>XGBClassifier</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>3.751700794390016</v>
-      </c>
-      <c r="O2" t="n">
-        <v>66</v>
-      </c>
-      <c r="P2" t="n">
-        <v>63</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>50</v>
-      </c>
-      <c r="R2" t="n">
-        <v>75</v>
-      </c>
-      <c r="S2" t="n">
-        <v>71</v>
-      </c>
-      <c r="T2" t="n">
-        <v>33</v>
-      </c>
-      <c r="U2" t="n">
-        <v>92</v>
-      </c>
-      <c r="V2" t="n">
-        <v>51.39664804469274</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>228</v>
-      </c>
-      <c r="B3" t="n">
-        <v>-1.18858559318555</v>
-      </c>
-      <c r="C3" t="n">
-        <v>1.239957012858478</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.9778454372858792</v>
-      </c>
-      <c r="E3" t="n">
-        <v>288.387955394816</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1.611105896060425</v>
-      </c>
-      <c r="G3" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>kelly</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>20</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>(179, 66)</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>XGBClassifier</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>0.2993239921651283</v>
-      </c>
-      <c r="O3" t="n">
-        <v>66</v>
-      </c>
-      <c r="P3" t="n">
-        <v>63</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>50</v>
-      </c>
-      <c r="R3" t="n">
-        <v>82</v>
-      </c>
-      <c r="S3" t="n">
-        <v>62</v>
-      </c>
-      <c r="T3" t="n">
-        <v>35</v>
-      </c>
-      <c r="U3" t="n">
-        <v>78</v>
-      </c>
-      <c r="V3" t="n">
-        <v>43.5754189944134</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p4_modeling/2024-10-15/df_best_model.xlsx
+++ b/data/italy/p4_modeling/2024-10-15/df_best_model.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:Q1"/>
+  <dimension ref="A1:Y3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,68 +446,282 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>roi_200</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>roi</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>roi_por_partido</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>thr_prob_min_best</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>curva</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>param1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>param2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>normalized</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>odd_weight</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>dif_prob_sup_cap</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>X_shape_missing</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>model_name</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>% roi_100</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t># result 1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t># result 0</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t># result 2</t>
         </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t># pred 1</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t># pred 0</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t># pred 2</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t># aciertos</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>precision</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>222</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-1.001036070581756</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.3714069860166683</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.054515807136114</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2.020078684284793</v>
+      </c>
+      <c r="F2" t="n">
+        <v>322.5781673820822</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.565913433893603</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>(206, 32)</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.216165804224605</v>
+      </c>
+      <c r="R2" t="n">
+        <v>79</v>
+      </c>
+      <c r="S2" t="n">
+        <v>67</v>
+      </c>
+      <c r="T2" t="n">
+        <v>60</v>
+      </c>
+      <c r="U2" t="n">
+        <v>90</v>
+      </c>
+      <c r="V2" t="n">
+        <v>66</v>
+      </c>
+      <c r="W2" t="n">
+        <v>50</v>
+      </c>
+      <c r="X2" t="n">
+        <v>95</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>46.11650485436893</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>268</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-1.05345516636612</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.5542729458984192</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.080147512484303</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.5897480056839245</v>
+      </c>
+      <c r="F3" t="n">
+        <v>130.3822370245019</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6329234807014656</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>(206, 40)</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>XGBClassifier</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>2.141898563487637</v>
+      </c>
+      <c r="R3" t="n">
+        <v>79</v>
+      </c>
+      <c r="S3" t="n">
+        <v>67</v>
+      </c>
+      <c r="T3" t="n">
+        <v>60</v>
+      </c>
+      <c r="U3" t="n">
+        <v>89</v>
+      </c>
+      <c r="V3" t="n">
+        <v>49</v>
+      </c>
+      <c r="W3" t="n">
+        <v>68</v>
+      </c>
+      <c r="X3" t="n">
+        <v>101</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>49.02912621359224</v>
       </c>
     </row>
   </sheetData>
